--- a/data/sub_fields.xlsx
+++ b/data/sub_fields.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="44">
   <si>
     <t>Parent Field</t>
   </si>
@@ -139,6 +139,18 @@
   </si>
   <si>
     <t>DG04006</t>
+  </si>
+  <si>
+    <t>Crop</t>
+  </si>
+  <si>
+    <t>Soil</t>
+  </si>
+  <si>
+    <t>Survey Date</t>
+  </si>
+  <si>
+    <t>Surveyor</t>
   </si>
 </sst>
 </file>
@@ -501,10 +513,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -512,233 +524,245 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="G1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
       <c r="B2" t="s">
         <v>5</v>
       </c>
-      <c r="C2">
+      <c r="E2">
         <v>3.01</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>27</v>
       </c>
-      <c r="C3">
+      <c r="E3">
         <v>1.1299999999999999</v>
       </c>
-      <c r="D3" t="s">
+      <c r="F3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>28</v>
       </c>
-      <c r="C4">
+      <c r="E4">
         <v>3.26</v>
       </c>
-      <c r="D4" t="s">
+      <c r="F4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>29</v>
       </c>
-      <c r="C5">
+      <c r="E5">
         <v>4.21</v>
       </c>
-      <c r="D5" t="s">
+      <c r="F5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>7</v>
       </c>
       <c r="B6" t="s">
         <v>30</v>
       </c>
-      <c r="C6">
+      <c r="E6">
         <v>4.66</v>
       </c>
-      <c r="D6" t="s">
+      <c r="F6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>7</v>
       </c>
       <c r="B7" t="s">
         <v>31</v>
       </c>
-      <c r="C7">
+      <c r="E7">
         <v>3.89</v>
       </c>
-      <c r="D7" t="s">
+      <c r="F7" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
       <c r="B8" t="s">
         <v>32</v>
       </c>
-      <c r="C8">
+      <c r="E8">
         <v>2.1800000000000002</v>
       </c>
-      <c r="D8" t="s">
+      <c r="F8" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>7</v>
       </c>
       <c r="B9" t="s">
         <v>33</v>
       </c>
-      <c r="C9">
+      <c r="E9">
         <v>0.75</v>
       </c>
-      <c r="D9" t="s">
+      <c r="F9" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>15</v>
       </c>
       <c r="B10" t="s">
         <v>34</v>
       </c>
-      <c r="C10">
+      <c r="E10">
         <v>0.97</v>
       </c>
-      <c r="D10" t="s">
+      <c r="F10" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>15</v>
       </c>
       <c r="B11" t="s">
         <v>35</v>
       </c>
-      <c r="C11">
+      <c r="E11">
         <v>2.92</v>
       </c>
-      <c r="D11" t="s">
+      <c r="F11" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>15</v>
       </c>
       <c r="B12" t="s">
         <v>36</v>
       </c>
-      <c r="C12">
+      <c r="E12">
         <v>4.7</v>
       </c>
-      <c r="D12" t="s">
+      <c r="F12" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>15</v>
       </c>
       <c r="B13" t="s">
         <v>37</v>
       </c>
-      <c r="C13">
+      <c r="E13">
         <v>4.41</v>
       </c>
-      <c r="D13" t="s">
+      <c r="F13" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>15</v>
       </c>
       <c r="B14" t="s">
         <v>38</v>
       </c>
-      <c r="C14">
+      <c r="E14">
         <v>2.68</v>
       </c>
-      <c r="D14" t="s">
+      <c r="F14" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>15</v>
       </c>
       <c r="B15" t="s">
         <v>39</v>
       </c>
-      <c r="C15">
+      <c r="E15">
         <v>0.75</v>
       </c>
-      <c r="D15" t="s">
+      <c r="F15" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>22</v>
       </c>
       <c r="B16" t="s">
         <v>23</v>
       </c>
-      <c r="C16">
+      <c r="E16">
         <v>3.36</v>
       </c>
-      <c r="D16" t="s">
+      <c r="F16" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>22</v>
       </c>
       <c r="B17" t="s">
         <v>25</v>
       </c>
-      <c r="C17">
+      <c r="E17">
         <v>3.02</v>
       </c>
-      <c r="D17" t="s">
+      <c r="F17" t="s">
         <v>26</v>
       </c>
     </row>

--- a/data/sub_fields.xlsx
+++ b/data/sub_fields.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="10695" windowHeight="7290"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7320"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="45">
+  <si>
+    <t>Survey ID</t>
+  </si>
   <si>
     <t>Parent Field</t>
   </si>
@@ -45,6 +48,51 @@
     <t>Surveyor</t>
   </si>
   <si>
+    <t>DG01000</t>
+  </si>
+  <si>
+    <t>DG01001</t>
+  </si>
+  <si>
+    <t>{"type": "Feature", "geometry": {"type": "Polygon", "coordinates": [[[34.119147, -12.517533], [34.119469, -12.517156], [34.11978742857143, -12.516793564995567], [34.11978742857143, -12.519075625350137], [34.11963, -12.518809], [34.118975, -12.517805], [34.119147, -12.517533]]]}}</t>
+  </si>
+  <si>
+    <t>DG01002</t>
+  </si>
+  <si>
+    <t>{"type": "Feature", "geometry": {"type": "Polygon", "coordinates": [[[34.120113, -12.516423], [34.12059985714286, -12.515880884280596], [34.12059985714286, -12.51994214746395], [34.120402, -12.520045], [34.120038, -12.5195], [34.11978742857143, -12.519075625350137], [34.11978742857143, -12.516793564995567], [34.120113, -12.516423]]]}}</t>
+  </si>
+  <si>
+    <t>DG01003</t>
+  </si>
+  <si>
+    <t>{"type": "Feature", "geometry": {"type": "Polygon", "coordinates": [[[34.12095, -12.515491], [34.121412285714285, -12.514957991471213], [34.121412285714285, -12.519519820841202], [34.12059985714286, -12.51994214746395], [34.12059985714286, -12.515880884280596], [34.12095, -12.515491]]]}}</t>
+  </si>
+  <si>
+    <t>DG01004</t>
+  </si>
+  <si>
+    <t>{"type": "Feature", "geometry": {"type": "Polygon", "coordinates": [[[34.121486, -12.514873], [34.121969, -12.51435], [34.122151, -12.514203], [34.122224714285714, -12.514311208226657], [34.122224714285714, -12.519097494218455], [34.121412285714285, -12.519519820841202], [34.121412285714285, -12.514957991471213], [34.121486, -12.514873]]]}}</t>
+  </si>
+  <si>
+    <t>DG01005</t>
+  </si>
+  <si>
+    <t>{"type": "Feature", "geometry": {"type": "Polygon", "coordinates": [[[34.122224714285714, -12.519097494218455], [34.122224714285714, -12.514311208226657], [34.12303714285714, -12.515503805484437], [34.12303714285714, -12.518675167595706], [34.122224714285714, -12.519097494218455]]]}}</t>
+  </si>
+  <si>
+    <t>DG01006</t>
+  </si>
+  <si>
+    <t>{"type": "Feature", "geometry": {"type": "Polygon", "coordinates": [[[34.123385, -12.518245], [34.123503, -12.518433], [34.12303714285714, -12.518675167595706], [34.12303714285714, -12.515503805484437], [34.12384957142857, -12.51669640274222], [34.12384957142857, -12.517994278911564], [34.123385, -12.518245]]]}}</t>
+  </si>
+  <si>
+    <t>DG01007</t>
+  </si>
+  <si>
+    <t>{"type": "Feature", "geometry": {"type": "Polygon", "coordinates": [[[34.124061, -12.518224], [34.123889, -12.517973], [34.12384957142857, -12.517994278911564], [34.12384957142857, -12.51669640274222], [34.124662, -12.517889], [34.124061, -12.518224]]]}}</t>
+  </si>
+  <si>
     <t>DG02000</t>
   </si>
   <si>
@@ -52,51 +100,6 @@
   </si>
   <si>
     <t>{"type":"Feature","properties":{},"geometry":{"type":"Polygon","coordinates":[[[34.123223,-12.521219],[34.122359,-12.520046],[34.121914,-12.519446],[34.12252,-12.519142],[34.123979,-12.518394],[34.123711,-12.519365],[34.123512,-12.520093],[34.123322,-12.520816],[34.123223,-12.521219]]]}}</t>
-  </si>
-  <si>
-    <t>DG01000</t>
-  </si>
-  <si>
-    <t>DG01001</t>
-  </si>
-  <si>
-    <t>{"type": "Feature", "geometry": {"type": "Polygon", "coordinates": [[[34.119147, -12.517533], [34.119469, -12.517156], [34.11978742857143, -12.516793564995567], [34.11978742857143, -12.519075625350137], [34.11963, -12.518809], [34.118975, -12.517805], [34.119147, -12.517533]]]}}</t>
-  </si>
-  <si>
-    <t>DG01002</t>
-  </si>
-  <si>
-    <t>{"type": "Feature", "geometry": {"type": "Polygon", "coordinates": [[[34.120113, -12.516423], [34.12059985714286, -12.515880884280596], [34.12059985714286, -12.51994214746395], [34.120402, -12.520045], [34.120038, -12.5195], [34.11978742857143, -12.519075625350137], [34.11978742857143, -12.516793564995567], [34.120113, -12.516423]]]}}</t>
-  </si>
-  <si>
-    <t>DG01003</t>
-  </si>
-  <si>
-    <t>{"type": "Feature", "geometry": {"type": "Polygon", "coordinates": [[[34.12095, -12.515491], [34.121412285714285, -12.514957991471213], [34.121412285714285, -12.519519820841202], [34.12059985714286, -12.51994214746395], [34.12059985714286, -12.515880884280596], [34.12095, -12.515491]]]}}</t>
-  </si>
-  <si>
-    <t>DG01004</t>
-  </si>
-  <si>
-    <t>{"type": "Feature", "geometry": {"type": "Polygon", "coordinates": [[[34.121486, -12.514873], [34.121969, -12.51435], [34.122151, -12.514203], [34.122224714285714, -12.514311208226657], [34.122224714285714, -12.519097494218455], [34.121412285714285, -12.519519820841202], [34.121412285714285, -12.514957991471213], [34.121486, -12.514873]]]}}</t>
-  </si>
-  <si>
-    <t>DG01005</t>
-  </si>
-  <si>
-    <t>{"type": "Feature", "geometry": {"type": "Polygon", "coordinates": [[[34.122224714285714, -12.519097494218455], [34.122224714285714, -12.514311208226657], [34.12303714285714, -12.515503805484437], [34.12303714285714, -12.518675167595706], [34.122224714285714, -12.519097494218455]]]}}</t>
-  </si>
-  <si>
-    <t>DG01006</t>
-  </si>
-  <si>
-    <t>{"type": "Feature", "geometry": {"type": "Polygon", "coordinates": [[[34.123385, -12.518245], [34.123503, -12.518433], [34.12303714285714, -12.518675167595706], [34.12303714285714, -12.515503805484437], [34.12384957142857, -12.51669640274222], [34.12384957142857, -12.517994278911564], [34.123385, -12.518245]]]}}</t>
-  </si>
-  <si>
-    <t>DG01007</t>
-  </si>
-  <si>
-    <t>{"type": "Feature", "geometry": {"type": "Polygon", "coordinates": [[[34.124061, -12.518224], [34.123889, -12.517973], [34.12384957142857, -12.517994278911564], [34.12384957142857, -12.51669640274222], [34.124662, -12.517889], [34.124061, -12.518224]]]}}</t>
   </si>
   <si>
     <t>DG04000</t>
@@ -513,10 +516,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -541,229 +544,232 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>9</v>
       </c>
-      <c r="E2">
-        <v>3.01</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="C2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="F2">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="G2" t="s">
         <v>11</v>
       </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
         <v>12</v>
       </c>
-      <c r="E3">
-        <v>1.1299999999999999</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="F3">
+        <v>3.26</v>
+      </c>
+      <c r="G3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>11</v>
-      </c>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
         <v>14</v>
       </c>
-      <c r="E4">
-        <v>3.26</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="F4">
+        <v>4.21</v>
+      </c>
+      <c r="G4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>11</v>
-      </c>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" t="s">
         <v>16</v>
       </c>
-      <c r="E5">
-        <v>4.21</v>
-      </c>
-      <c r="F5" t="s">
+      <c r="F5">
+        <v>4.66</v>
+      </c>
+      <c r="G5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>11</v>
-      </c>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" t="s">
         <v>18</v>
       </c>
-      <c r="E6">
-        <v>4.66</v>
-      </c>
-      <c r="F6" t="s">
+      <c r="F6">
+        <v>3.89</v>
+      </c>
+      <c r="G6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>11</v>
-      </c>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" t="s">
         <v>20</v>
       </c>
-      <c r="E7">
-        <v>3.89</v>
-      </c>
-      <c r="F7" t="s">
+      <c r="F7">
+        <v>2.1800000000000002</v>
+      </c>
+      <c r="G7" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>11</v>
-      </c>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" t="s">
         <v>22</v>
       </c>
-      <c r="E8">
-        <v>2.1800000000000002</v>
-      </c>
-      <c r="F8" t="s">
+      <c r="F8">
+        <v>0.75</v>
+      </c>
+      <c r="G8" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>11</v>
-      </c>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>24</v>
       </c>
-      <c r="E9">
-        <v>0.75</v>
-      </c>
-      <c r="F9" t="s">
+      <c r="C9" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="F9">
+        <v>3.01</v>
+      </c>
+      <c r="G9" t="s">
         <v>26</v>
       </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>27</v>
       </c>
-      <c r="E10">
+      <c r="C10" t="s">
+        <v>28</v>
+      </c>
+      <c r="F10">
         <v>0.97</v>
       </c>
-      <c r="F10" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>26</v>
-      </c>
+      <c r="G10" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>29</v>
-      </c>
-      <c r="E11">
+        <v>27</v>
+      </c>
+      <c r="C11" t="s">
+        <v>30</v>
+      </c>
+      <c r="F11">
         <v>2.92</v>
       </c>
-      <c r="F11" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>26</v>
-      </c>
+      <c r="G11" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>31</v>
-      </c>
-      <c r="E12">
+        <v>27</v>
+      </c>
+      <c r="C12" t="s">
+        <v>32</v>
+      </c>
+      <c r="F12">
         <v>4.7</v>
       </c>
-      <c r="F12" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>26</v>
-      </c>
+      <c r="G12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>33</v>
-      </c>
-      <c r="E13">
+        <v>27</v>
+      </c>
+      <c r="C13" t="s">
+        <v>34</v>
+      </c>
+      <c r="F13">
         <v>4.41</v>
       </c>
-      <c r="F13" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>26</v>
-      </c>
+      <c r="G13" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>35</v>
-      </c>
-      <c r="E14">
+        <v>27</v>
+      </c>
+      <c r="C14" t="s">
+        <v>36</v>
+      </c>
+      <c r="F14">
         <v>2.68</v>
       </c>
-      <c r="F14" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>26</v>
-      </c>
+      <c r="G14" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>37</v>
-      </c>
-      <c r="E15">
+        <v>27</v>
+      </c>
+      <c r="C15" t="s">
+        <v>38</v>
+      </c>
+      <c r="F15">
         <v>0.75</v>
       </c>
-      <c r="F15" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+      <c r="G15" t="s">
         <v>39</v>
       </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>40</v>
       </c>
-      <c r="E16">
+      <c r="C16" t="s">
+        <v>41</v>
+      </c>
+      <c r="F16">
         <v>3.36</v>
       </c>
-      <c r="F16" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>39</v>
-      </c>
+      <c r="G16" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>42</v>
-      </c>
-      <c r="E17">
+        <v>40</v>
+      </c>
+      <c r="C17" t="s">
+        <v>43</v>
+      </c>
+      <c r="F17">
         <v>3.02</v>
       </c>
-      <c r="F17" t="s">
-        <v>43</v>
+      <c r="G17" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
